--- a/data/product_usage_guide.xlsx
+++ b/data/product_usage_guide.xlsx
@@ -4104,23 +4104,23 @@
           <t>spread</t>
         </is>
       </c>
-      <c r="Q30" s="5" t="n">
-        <v>1</v>
+      <c r="Q30" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="R30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v>1</v>
+      <c r="S30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0</v>

--- a/data/product_usage_guide.xlsx
+++ b/data/product_usage_guide.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'products'!$A$1:$AD$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'rates'!$A$1:$F$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'rates'!$A$1:$F$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -269,8 +269,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Rates" displayName="Rates" ref="A1:F80" headerRowCount="1">
-  <autoFilter ref="A1:F80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Rates" displayName="Rates" ref="A1:F85" headerRowCount="1">
+  <autoFilter ref="A1:F85"/>
   <tableColumns count="6">
     <tableColumn id="1" name="sku"/>
     <tableColumn id="2" name="guide_name"/>
@@ -1559,7 +1559,7 @@
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Apply every 4 weeks during active growth. Vegetables can be applied fortnightly when actively producing. Trees, fruit and vines can be applied every 6–8 weeks as required.</t>
+          <t>Apply every 4 weeks during flowering/fruiting. Vegetables can be applied fortnightly when actively producing. Trees, fruit and vines can be applied every 6–8 weeks as required.</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
@@ -2054,8 +2054,8 @@
       <c r="R12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="6" t="n">
-        <v>1</v>
+      <c r="S12" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AA12" s="4" t="inlineStr">
         <is>
-          <t>Apply evenly by hand or broadcast spreader, then water in to activate. Suitable for lawns, vegetables, fruit trees, crops, ornamentals and all soil types. Can be applied alongside fertilisers, side dressing, seeding and planting.</t>
+          <t>Apply evenly by hand or broadcast spreader onto the top layer of soil, under mulch, or dug in. Does not need to be watered in. Suitable for lawns, vegetables, fruit trees, crops, ornamentals and all soil types. Can be applied alongside fertilisers, side dressing, seeding and planting.</t>
         </is>
       </c>
       <c r="AB12" s="4" t="inlineStr">
@@ -2925,10 +2925,14 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Varies by application type.</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
+          <t>Home garden: 45 mL in 9 L water, apply 1 L/m² (500 mL per 100 m²). Soil ameliorant or fertigation: 10–50 L/ha. Foliar: 1 L per 100 L water, up to 5–7 L/ha depending on crop.</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Apply every 2–4 weeks, or as required, to improve clay soils, correct calcium and sulphur deficiencies, and support ongoing soil conditioning. Higher rates for heavy clay soils.</t>
@@ -2976,8 +2980,8 @@
       <c r="T20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="U20" s="4" t="n">
-        <v>0</v>
+      <c r="U20" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="V20" s="8" t="n">
         <v>1</v>
@@ -2996,7 +3000,7 @@
       </c>
       <c r="AA20" s="4" t="inlineStr">
         <is>
-          <t>Shake well before use and maintain constant agitation. Can be applied through fertigation, watering cans or spray equipment. A coarse filter is recommended, and a jar test should be performed before mixing. Not suitable for drippers.</t>
+          <t>Shake or stir well before use and keep agitating. Pre-mix slowly. Will pass a 200-micron filter under ideal conditions; a coarse inline filter (500 micron / 35 mesh) is recommended. Drench with a watering can or equipment that can take larger particles. Not suitable for drippers. Foliar use can leave a visible residue on leaves and fruit. Jar test before mixing. Liquid inject minimum dilution 1-part product to 3-parts water. Store cool and keep sealed.</t>
         </is>
       </c>
       <c r="AB20" s="4" t="inlineStr">
@@ -4396,7 +4400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5915,7 +5919,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Apply at 1 L/m²</t>
+          <t>Apply 1 L/m² every 2–4 weeks (500 mL per 100 m²)</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5949,11 @@
           <t>10–50 L/ha</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Use higher rates for heavy clay</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -5960,221 +5968,241 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
+          <t>foliar_vegetables</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
           <t>foliar</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>foliar</t>
-        </is>
-      </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>1 L per 100 L water</t>
+          <t>1 L per 100 L water, up to 5 L/ha</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Rate varies by crop</t>
+          <t>Weekly or as required</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>NSWL</t>
+          <t>636</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Nature's Soil Wetter - Liquid</t>
+          <t>Micronised Gypsum Liquid</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>lawn_garden</t>
+          <t>foliar_orchards_vineyards</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>spray</t>
+          <t>foliar</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>100 mL / 100 m²</t>
+          <t>1 L per 100 L water, up to 7 L/ha</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Do not shake</t>
+          <t>Every 2–4 weeks or as required</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>636</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Nature's Soil Wetter granules</t>
+          <t>Micronised Gypsum Liquid</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>lawns_gardens</t>
+          <t>foliar_ornamentals_turf</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>foliar</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>1.5–2 kg / 100 m² every 3–6 months</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr"/>
+          <t>1 L per 100 L water, up to 5 L/ha</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Every 2–4 weeks or as required</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>636</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Nature's Soil Wetter granules</t>
+          <t>Micronised Gypsum Liquid</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>golf_greens</t>
+          <t>broadacre_crops_pasture</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>spray</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>1.5 kg / 100 m² every 1–2 months</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
+          <t>1–3 L/ha in 60–100 L water</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Depending on canopy closure</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>636</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Nature's Soil Wetter granules</t>
+          <t>Micronised Gypsum Liquid</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>fairways_sports</t>
+          <t>spot_spraying</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>spray</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2 kg / 100 m² every 2–3 months</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr"/>
+          <t>50 mL per 10 L water</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Apply as required</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>636</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Nature's Soil Wetter granules</t>
+          <t>Micronised Gypsum Liquid</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>crops_vegetables</t>
+          <t>liquid_inject</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>inject</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>1.5–2 kg / 100 m²</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr"/>
+          <t>2–5 L/ha</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Minimum dilution 1:3</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>NSWL</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Neem Fertiliser Slow Release Granules</t>
+          <t>Nature's Soil Wetter - Liquid</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>soil_amendment</t>
+          <t>lawn_garden</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>spray</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>50–100 g/m²</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr"/>
+          <t>100 mL / 100 m²</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Do not shake</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>NSO</t>
+          <t>664</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Neem Seed Oil - 100% Cold Pressed virgin oil</t>
+          <t>Nature's Soil Wetter granules</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>garden</t>
+          <t>lawns_gardens</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>foliar</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>30 mL per 1 L water + a few drops biodegradable detergent</t>
+          <t>1.5–2 kg / 100 m² every 3–6 months</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr"/>
@@ -6182,59 +6210,55 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>NSO</t>
+          <t>664</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Neem Seed Oil - 100% Cold Pressed virgin oil</t>
+          <t>Nature's Soil Wetter granules</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>golf_greens</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>spray</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>1 L neem oil per 200 L water</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>Apply 2–3 L prepared spray per hectare</t>
-        </is>
-      </c>
+          <t>1.5 kg / 100 m² every 1–2 months</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>29800</t>
+          <t>664</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Quantum H</t>
+          <t>Nature's Soil Wetter granules</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>home_garden</t>
+          <t>fairways_sports</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>spray</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>100 mL / 100 m²</t>
+          <t>2 kg / 100 m² every 2–3 months</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
@@ -6242,27 +6266,27 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>29782</t>
+          <t>664</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Rescue Remedy</t>
+          <t>Nature's Soil Wetter granules</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>crops_vegetables</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>spray</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>10 g / 10 L water or 10 g / 100 m²</t>
+          <t>1.5–2 kg / 100 m²</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
@@ -6270,17 +6294,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>758</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Roots, Shoots &amp; Leaves - Granular</t>
+          <t>Neem Fertiliser Slow Release Granules</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>lawn</t>
+          <t>soil_amendment</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6290,7 +6314,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>20–40 g/m²</t>
+          <t>50–100 g/m²</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
@@ -6298,27 +6322,27 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>NSO</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Roots, Shoots &amp; Leaves - Granular</t>
+          <t>Neem Seed Oil - 100% Cold Pressed virgin oil</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>pots</t>
+          <t>garden</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>incorporate</t>
+          <t>foliar</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>4 g per litre of potting mix</t>
+          <t>30 mL per 1 L water + a few drops biodegradable detergent</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -6326,40 +6350,44 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>NSO</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Roots, Shoots &amp; Leaves - Granular</t>
+          <t>Neem Seed Oil - 100% Cold Pressed virgin oil</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>plants_gardens</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>spray</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>varies with plant type and size</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr"/>
+          <t>1 L neem oil per 200 L water</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Apply 2–3 L prepared spray per hectare</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Seaweed Secrets</t>
+          <t>Quantum H</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -6382,17 +6410,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>29782</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Stimulizer</t>
+          <t>Rescue Remedy</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>home_garden_area</t>
+          <t>general</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -6402,7 +6430,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>3 mL / 100 m²</t>
+          <t>10 g / 10 L water or 10 g / 100 m²</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr"/>
@@ -6410,27 +6438,27 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Stimulizer</t>
+          <t>Roots, Shoots &amp; Leaves - Granular</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>watering_can</t>
+          <t>lawn</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>drench</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2 mL per 9 L watering can</t>
+          <t>20–40 g/m²</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr"/>
@@ -6438,27 +6466,27 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>VolcaMin – Premium Clinoptilolite Zeolite</t>
+          <t>Roots, Shoots &amp; Leaves - Granular</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>lawn_garden</t>
+          <t>pots</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>incorporate</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>25–100 g/m²</t>
+          <t>4 g per litre of potting mix</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr"/>
@@ -6466,27 +6494,27 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>VolcaMin – Premium Clinoptilolite Zeolite</t>
+          <t>Roots, Shoots &amp; Leaves - Granular</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>potting_mix</t>
+          <t>plants_gardens</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>incorporate</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>5% by volume (~50 L per m³)</t>
+          <t>varies with plant type and size</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr"/>
@@ -6494,27 +6522,27 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>VolcaMin – Premium Clinoptilolite Zeolite</t>
+          <t>Seaweed Secrets</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>soil_amendment</t>
+          <t>home_garden</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>spray</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>1–5 tonnes/ha</t>
+          <t>100 mL / 100 m²</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr"/>
@@ -6522,27 +6550,27 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>VolcaMin – Premium Clinoptilolite Zeolite</t>
+          <t>Stimulizer</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>tree_planting</t>
+          <t>home_garden_area</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>incorporate</t>
+          <t>spray</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>5–10 kg per planting hole or 3–5 kg per tree for trenching</t>
+          <t>3 mL / 100 m²</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr"/>
@@ -6550,27 +6578,27 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>WMP</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Worm Magic Casting Pellets</t>
+          <t>Stimulizer</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>lawns_gardens</t>
+          <t>watering_can</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>drench</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>20–40 g/m²</t>
+          <t>2 mL per 9 L watering can</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr"/>
@@ -6578,91 +6606,83 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>WMP</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Worm Magic Casting Pellets</t>
+          <t>VolcaMin – Premium Clinoptilolite Zeolite</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>pots</t>
+          <t>lawn_garden</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>incorporate</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2 tablespoons per 5 L potting mix</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>Every 4–6 weeks</t>
-        </is>
-      </c>
+          <t>25–100 g/m²</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>WMP</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Worm Magic Casting Pellets</t>
+          <t>VolcaMin – Premium Clinoptilolite Zeolite</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>potting_mix</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>incorporate</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>100–1000 kg/ha</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>Varies by crop</t>
-        </is>
-      </c>
+          <t>5% by volume (~50 L per m³)</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Worm Magic Liquid Compost Tea</t>
+          <t>VolcaMin – Premium Clinoptilolite Zeolite</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>garden_beds_small_lawns</t>
+          <t>soil_amendment</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>drench</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>50–100 mL per 9 L water</t>
+          <t>1–5 tonnes/ha</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr"/>
@@ -6670,27 +6690,27 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>557</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Worm Magic Liquid Compost Tea</t>
+          <t>VolcaMin – Premium Clinoptilolite Zeolite</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>pots</t>
+          <t>tree_planting</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>drench</t>
+          <t>incorporate</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>10–20 mL per litre water</t>
+          <t>5–10 kg per planting hole or 3–5 kg per tree for trenching</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr"/>
@@ -6698,33 +6718,181 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
+          <t>WMP</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Worm Magic Casting Pellets</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>lawns_gardens</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>20–40 g/m²</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>WMP</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Worm Magic Casting Pellets</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>pots</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>incorporate</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>2 tablespoons per 5 L potting mix</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Every 4–6 weeks</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>WMP</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Worm Magic Casting Pellets</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>agriculture</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>100–1000 kg/ha</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Varies by crop</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
           <t>WMB</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>Worm Magic Liquid Compost Tea</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>garden_beds_small_lawns</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>drench</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>50–100 mL per 9 L water</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>WMB</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Worm Magic Liquid Compost Tea</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>pots</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>drench</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>10–20 mL per litre water</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>WMB</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Worm Magic Liquid Compost Tea</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>fruit_trees_shrubs</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>drench</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t>100–150 mL per 9 L water</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F80"/>
+  <autoFilter ref="A1:F85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
